--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R5e7d08b4e25845a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R3222c38e423a4f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Ref69f904e61e4634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rcb602c7aed2b4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R0e0b039820a44822"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R7083dd11afc04d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="Rca72e8c42e4f4b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R9484a8f7fb864c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="Rd026aa37fe304686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R826c5942c8e149dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Rd6cc521330084c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R22052c543b604361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R00f62da7cdb94bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R1352ebabfb084b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rad431ca53a194ae0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Re73aa3a8a85546c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R12a560fadd504993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R4548d21c509940bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Rfdfd868e68164c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R1d11919ec92d44db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R465926a4ea79427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R40af13e9baa84f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R04ff76e7f99a44f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rf32115cae53c40e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Rce6898a1382b419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R48914bcd511f4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R8f708452330543ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R2a743f640371496c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -110,9 +110,6 @@
     <x:t xml:space="preserve">高频筛选字段建索引</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">用户状态、角色删除标记、菜单路径、工单状态/跟进人、档案类型、操作日志对象建索引。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">时间类型</x:t>
   </x:si>
   <x:si>
@@ -1109,15 +1106,9 @@
     <x:t xml:space="preserve">appearance_mode</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">system</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">light</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">外观模式兼容字段；当前界面已删除外观模式，服务端统一归到 light。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">UNIQUE(user_id)</x:t>
   </x:si>
   <x:si>
@@ -1164,9 +1155,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">导出文件已生成，可前往相关页面查看结果。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">消息正文描述。</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">跳转路径</x:t>
@@ -2385,38 +2373,38 @@
       <x:c r="B10" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>29</x:v>
+      <x:c r="C10" s="16" t="str">
+        <x:v>用户状态、角色删除标记、菜单路径、工单状态/跟进人、档案类型、操作日志模块与创建时间建索引。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A12" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B12" s="16" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A13" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B13" s="16" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="16" t="str">
         <x:v>初始化 SQL 包含管理员、业务菜单、组件工作台独立子菜单和基础档案。</x:v>
@@ -2456,7 +2444,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2470,328 +2458,328 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>267</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="C7" s="7" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
+      <x:c r="C9" s="7" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I12" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I12" s="9" t="s">
+      <x:c r="J12" s="9" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J12" s="9" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I13" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I13" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2821,7 +2809,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2835,312 +2823,312 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>155</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D4" s="7"/>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>274</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>278</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>282</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H7" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>285</x:v>
-      </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>286</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>292</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>300</x:v>
-      </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="J12" s="9" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="J12" s="9" t="s">
-        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I13" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I13" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3170,7 +3158,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3184,440 +3172,440 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>155</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D4" s="7"/>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="C5" s="7" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="D5" s="7"/>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H5" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I5" s="8" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>308</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="I6" s="8" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>314</x:v>
-      </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>318</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>314</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
       <x:c r="I9" s="8" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>326</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>330</x:v>
-      </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>333</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="J13" s="9" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="A14" s="9" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>337</x:v>
-      </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="9"/>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I14" s="9" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="J14" s="9" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>339</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="A15" s="9" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>341</x:v>
-      </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I15" s="10">
         <x:v>3600</x:v>
       </x:c>
       <x:c r="J15" s="9" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="A16" s="9" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B16" s="9" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D16" s="9"/>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I16" s="9" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="J16" s="9" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="A17" s="9" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="B17" s="9" t="s">
-        <x:v>347</x:v>
-      </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D17" s="9"/>
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="9"/>
       <x:c r="G17" s="9"/>
       <x:c r="H17" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I17" s="9" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="J17" s="9" t="s">
         <x:v>348</x:v>
-      </x:c>
-      <x:c r="J17" s="9" t="s">
-        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="A18" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B18" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D18" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9"/>
       <x:c r="G18" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H18" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I18" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I18" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J18" s="9" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3647,7 +3635,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3661,134 +3649,134 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>155</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>354</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>355</x:v>
-      </x:c>
-      <x:c r="I5" s="8" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>358</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
@@ -3800,85 +3788,85 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>359</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>361</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7" t="s">
-        <x:v>362</x:v>
+      <x:c r="H7" s="7" t="str">
+        <x:v>light</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>364</x:v>
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="str">
+        <x:v>外观模式，当前仅支持浅色。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="s">
+      <x:c r="J8" s="7" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I9" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I9" s="8" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
@@ -3898,29 +3886,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>365</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F11" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="8" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>366</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3950,354 +3938,354 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="G1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="J1" s="5" t="s">
-        <x:v>367</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>368</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>369</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>314</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>373</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>374</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>375</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>376</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
-        <x:v>377</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>378</x:v>
+        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>379</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="8" t="s">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="str">
+        <x:v>消息正文，最长 1000 个字符。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="C10" s="7" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A12" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E12" s="7"/>
       <x:c r="F12" s="7"/>
       <x:c r="G12" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H12" s="7" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I12" s="8" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A13" s="7" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C13" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E13" s="7"/>
       <x:c r="F13" s="7"/>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I13" s="8" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="J13" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4321,13 +4309,13 @@
   <x:sheetData>
     <x:row r="1" s="12" customFormat="1">
       <x:c r="A1" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="s">
+      <x:c r="C1" s="13" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="C1" s="13" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
         <x:v>2</x:v>
@@ -4338,13 +4326,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="s">
+      <x:c r="D2" s="9" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4352,13 +4340,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="s">
+      <x:c r="D3" s="9" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4366,13 +4354,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="s">
+      <x:c r="D4" s="9" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4380,13 +4368,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="s">
+      <x:c r="D5" s="9" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4394,13 +4382,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="s">
+      <x:c r="D6" s="9" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4408,13 +4396,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="s">
+      <x:c r="D7" s="9" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4422,13 +4410,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4436,13 +4424,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="s">
+      <x:c r="D9" s="9" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4450,13 +4438,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="s">
+      <x:c r="D10" s="9" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4464,13 +4452,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C11" s="9" t="s">
+      <x:c r="D11" s="9" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="s">
-        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4478,13 +4466,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C12" s="9" t="s">
+      <x:c r="D12" s="9" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4492,19 +4480,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="s">
+      <x:c r="D13" s="9" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1066e06df64657"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re63836892bf74abf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4528,7 +4516,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -4542,352 +4530,378 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="C4" s="7" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
+      <x:c r="C6" s="7" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D6" s="7"/>
+      <x:c r="D6" s="7" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="C7" s="7" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="C10" s="7" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H12" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I12" s="10">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I13" s="10" t="s">
+      <x:c r="J13" s="9" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I14" s="10" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J14" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>头像地址</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>avatar_url</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>VARCHAR(300)</x:v>
+      </x:c>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>/uploads/avatars/1.png</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>用户头像访问地址。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4917,7 +4931,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -4931,272 +4945,272 @@
     </x:row>
     <x:row r="2" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>143</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
+      <x:c r="C6" s="7" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="D6" s="7"/>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="C7" s="7" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H9" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I10" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="s">
+      <x:c r="J10" s="7" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="11" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5226,7 +5240,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5240,150 +5254,150 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>155</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="C5" s="7" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E5" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F5" s="7" t="s">
-        <x:v>159</x:v>
-      </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
@@ -5403,29 +5417,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
+      <x:c r="D8" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>166</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5455,7 +5469,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5469,137 +5483,137 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>169</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="str">
@@ -5611,48 +5625,48 @@
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>177</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>180</x:v>
-      </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>/system/design-system?category=base</x:v>
@@ -5663,46 +5677,46 @@
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>182</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="C10" s="7" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I10" s="8" t="n">
         <x:v>45</x:v>
@@ -5713,160 +5727,160 @@
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
+      <x:c r="C11" s="7" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
+      <x:c r="C12" s="9" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I13" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D14" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H14" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I14" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I15" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I15" s="9" t="s">
+      <x:c r="J15" s="9" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D16" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I16" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I16" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J16" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5896,7 +5910,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5910,150 +5924,150 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="C4" s="7" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>159</x:v>
-      </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
@@ -6073,29 +6087,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>194</x:v>
-      </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>196</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6125,7 +6139,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>197</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -6139,552 +6153,552 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>201</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7" t="s">
-        <x:v>200</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>204</x:v>
+        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
+      <x:c r="C6" s="7" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>207</x:v>
-      </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>211</x:v>
-      </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>215</x:v>
-      </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="C10" s="7" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H10" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>222</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>223</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="17">
       <x:c r="A12" s="7" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="s">
-        <x:v>225</x:v>
-      </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="7"/>
       <x:c r="E12" s="7"/>
       <x:c r="F12" s="7"/>
       <x:c r="G12" s="7"/>
       <x:c r="H12" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="8" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="s">
-        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>229</x:v>
-      </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>232</x:v>
-      </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D14" s="9"/>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I14" s="9" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="J14" s="9" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>236</x:v>
-      </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9"/>
       <x:c r="I15" s="9" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="J15" s="9" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="s">
+      <x:c r="C16" s="9" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="C16" s="9" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="D16" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9"/>
       <x:c r="I16" s="9" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="J16" s="9" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="B17" s="9" t="s">
-        <x:v>245</x:v>
-      </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="9"/>
       <x:c r="G17" s="9"/>
       <x:c r="H17" s="9"/>
       <x:c r="I17" s="9" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="J17" s="9" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="J17" s="9" t="s">
-        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="9" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B18" s="9" t="s">
+      <x:c r="C18" s="9" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D18" s="9"/>
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G18" s="9"/>
       <x:c r="H18" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I18" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="9" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="9" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B19" s="9" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C19" s="9" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D19" s="9"/>
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G19" s="9"/>
       <x:c r="H19" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I19" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J19" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B20" s="9" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C20" s="9" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D20" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E20" s="9"/>
       <x:c r="F20" s="9"/>
       <x:c r="G20" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H20" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I20" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J20" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B21" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C21" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D21" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E21" s="9"/>
       <x:c r="F21" s="9"/>
       <x:c r="G21" s="9"/>
       <x:c r="H21" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I21" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I21" s="9" t="s">
+      <x:c r="J21" s="9" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J21" s="9" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B22" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C22" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D22" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E22" s="9"/>
       <x:c r="F22" s="9"/>
       <x:c r="G22" s="9"/>
       <x:c r="H22" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I22" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I22" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J22" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6714,7 +6728,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -6728,302 +6742,302 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="C2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
+      <x:c r="C3" s="7" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>249</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>253</x:v>
-      </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="C7" s="7" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H10" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I11" s="8" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="s">
+      <x:c r="J11" s="7" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I12" s="9" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="I12" s="9" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rad431ca53a194ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Re73aa3a8a85546c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R12a560fadd504993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R4548d21c509940bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Rfdfd868e68164c08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R1d11919ec92d44db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R465926a4ea79427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R40af13e9baa84f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R04ff76e7f99a44f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rf32115cae53c40e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Rce6898a1382b419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R48914bcd511f4443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R8f708452330543ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R2a743f640371496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rd40198d6f67f44f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R0239707e36184be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R2426dc62deb748b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rf4b784e5da244ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R237e65893a06434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R56b778ce8e1f4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R38dbdf9f249c4ed9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="Rdcad48a3d8e94dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R5a2e20d2154a47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R43b3fbbea4404882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R24a613988c8b4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Rd03b6ad23d484af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R63f0a904052e4e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Ra6082f9ea4f84b70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -645,9 +645,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">新员工账号权限开通</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">工单问题描述。</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">处置结果</x:t>
@@ -2444,7 +2441,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2520,13 +2517,13 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>90</x:v>
@@ -2540,21 +2537,21 @@
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>90</x:v>
@@ -2564,18 +2561,18 @@
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
         <x:v>121</x:v>
@@ -2585,7 +2582,7 @@
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G6" s="7" t="s">
         <x:v>90</x:v>
@@ -2595,7 +2592,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
@@ -2621,7 +2618,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
@@ -2809,7 +2806,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2906,15 +2903,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
         <x:v>95</x:v>
@@ -2927,18 +2924,18 @@
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
         <x:v>95</x:v>
@@ -2953,18 +2950,18 @@
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
         <x:v>121</x:v>
@@ -2982,15 +2979,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
         <x:v>149</x:v>
@@ -3006,18 +3003,18 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>287</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
@@ -3027,18 +3024,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>289</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
         <x:v>206</x:v>
@@ -3051,18 +3048,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>293</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
         <x:v>206</x:v>
@@ -3075,18 +3072,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>297</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
         <x:v>95</x:v>
@@ -3099,10 +3096,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="J12" s="9" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="J12" s="9" t="s">
-        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
@@ -3128,7 +3125,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>302</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3158,7 +3155,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3255,7 +3252,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
@@ -3281,18 +3278,18 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>307</x:v>
-      </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>90</x:v>
@@ -3301,13 +3298,13 @@
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
         <x:v>96</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
@@ -3331,18 +3328,18 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+      <x:c r="C8" s="7" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>313</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
         <x:v>90</x:v>
@@ -3352,21 +3349,21 @@
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
         <x:v>314</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>315</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>317</x:v>
-      </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
         <x:v>90</x:v>
@@ -3376,21 +3373,21 @@
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
       <x:c r="I9" s="8" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>319</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>321</x:v>
-      </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
@@ -3400,21 +3397,21 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>323</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>325</x:v>
-      </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7" t="s">
@@ -3428,18 +3425,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
         <x:v>30</x:v>
@@ -3455,15 +3452,15 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>331</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>332</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
         <x:v>30</x:v>
@@ -3476,18 +3473,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="J13" s="9" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="A14" s="9" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
         <x:v>30</x:v>
@@ -3500,18 +3497,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I14" s="9" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="J14" s="9" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="A15" s="9" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
         <x:v>339</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>340</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
         <x:v>186</x:v>
@@ -3529,18 +3526,18 @@
         <x:v>3600</x:v>
       </x:c>
       <x:c r="J15" s="9" t="s">
-        <x:v>341</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="A16" s="9" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B16" s="9" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D16" s="9"/>
       <x:c r="E16" s="9"/>
@@ -3550,18 +3547,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I16" s="9" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="J16" s="9" t="s">
         <x:v>343</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="A17" s="9" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
         <x:v>345</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="s">
-        <x:v>346</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
         <x:v>206</x:v>
@@ -3574,10 +3571,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I17" s="9" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="J17" s="9" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="J17" s="9" t="s">
-        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
@@ -3605,7 +3602,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="J18" s="9" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3635,7 +3632,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3736,15 +3733,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>352</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>353</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
         <x:v>149</x:v>
@@ -3756,21 +3753,21 @@
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="I5" s="8" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="I5" s="8" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>356</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>357</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
         <x:v>186</x:v>
@@ -3788,15 +3785,15 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
         <x:v>104</x:v>
@@ -3811,7 +3808,7 @@
         <x:v>light</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
         <x:v>外观模式，当前仅支持浅色。</x:v>
@@ -3886,7 +3883,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>362</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
         <x:v>162</x:v>
@@ -3908,7 +3905,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3938,34 +3935,34 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="G1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="J1" s="5" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
@@ -4032,10 +4029,10 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>366</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
         <x:v>121</x:v>
@@ -4055,18 +4052,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>368</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>90</x:v>
@@ -4076,21 +4073,21 @@
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>369</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="s">
+      <x:c r="C6" s="7" t="s">
         <x:v>372</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>373</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>90</x:v>
@@ -4100,15 +4097,15 @@
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>374</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>375</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
         <x:v>148</x:v>
@@ -4124,7 +4121,7 @@
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="8" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
         <x:v>消息正文，最长 1000 个字符。</x:v>
@@ -4132,10 +4129,10 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>378</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>379</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
         <x:v>149</x:v>
@@ -4148,18 +4145,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>380</x:v>
+        <x:v>379</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>382</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
         <x:v>30</x:v>
@@ -4174,10 +4171,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="s">
         <x:v>383</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
@@ -4203,7 +4200,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
@@ -4256,7 +4253,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="I12" s="8" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="J12" s="7" t="s">
         <x:v>136</x:v>
@@ -4282,7 +4279,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="I13" s="8" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="J13" s="7" t="s">
         <x:v>139</x:v>
@@ -4492,7 +4489,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re63836892bf74abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788f66b8ccf94cd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6282,23 +6279,27 @@
       <x:c r="D6" s="7" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E6" s="7"/>
+      <x:c r="E6" s="7" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7"/>
+      <x:c r="G6" s="7" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>208</x:v>
+      <x:c r="J6" s="7" t="str">
+        <x:v>工单问题描述；有效数据（is_deleted = 0）按 md5(problem_desc) 唯一。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
         <x:v>206</x:v>
@@ -6311,18 +6312,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
         <x:v>121</x:v>
@@ -6342,15 +6343,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
         <x:v>113</x:v>
@@ -6368,7 +6369,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
@@ -6396,15 +6397,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
         <x:v>113</x:v>
@@ -6422,15 +6423,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="17">
       <x:c r="A12" s="7" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
         <x:v>30</x:v>
@@ -6443,18 +6444,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I12" s="8" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="s">
-        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
         <x:v>30</x:v>
@@ -6467,18 +6468,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
         <x:v>30</x:v>
@@ -6491,18 +6492,18 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="I14" s="9" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="J14" s="9" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
         <x:v>95</x:v>
@@ -6515,21 +6516,21 @@
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9"/>
       <x:c r="I15" s="9" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="J15" s="9" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="s">
+      <x:c r="C16" s="9" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="D16" s="9" t="s">
         <x:v>90</x:v>
@@ -6539,18 +6540,18 @@
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9"/>
       <x:c r="I16" s="9" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="J16" s="9" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="9" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
         <x:v>30</x:v>
@@ -6563,10 +6564,10 @@
       <x:c r="G17" s="9"/>
       <x:c r="H17" s="9"/>
       <x:c r="I17" s="9" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="J17" s="9" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="J17" s="9" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6728,7 +6729,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -6804,7 +6805,7 @@
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
         <x:v>142</x:v>
@@ -6824,18 +6825,18 @@
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
         <x:v>104</x:v>
@@ -6852,21 +6853,21 @@
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>90</x:v>
@@ -6876,10 +6877,10 @@
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rd30e3fa941b44403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R9a66996217124dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Rb0748ef8007d49e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rdd67fbce6e804a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R82eb2f18fc114b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Re04ccba0fe7c4d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R7434f07979934eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R60bedb98fa3d4381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="Rb0e9625dfc6c49e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rc4b58edc76b0483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R25c88550db684b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Rd6c2e05cbc3745d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="Rbb6ede752ec047a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R24e20227f7e64689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R31ab925aae114aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R911d3699bc8b4633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Raf50efc9a88a4060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R45100af8d97e4b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Rba0f746606644abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Re60dc8879eb647b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R54c0babcfab149f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R184155968ff94e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R087080d13b5c4772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R77f400d310ec472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R3dd889983e1246a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R0e939b74521545e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R396457299e2d4cc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Rc3a715286a454ccf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -98,12 +98,6 @@
     <x:t xml:space="preserve">唯一约束</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">UNIQUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">业务编码、手机号、关联关系等按实际规则设置唯一约束。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">索引策略</x:t>
   </x:si>
   <x:si>
@@ -452,9 +446,6 @@
     <x:t xml:space="preserve">code</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">角色业务编码。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">角色名称</x:t>
   </x:si>
   <x:si>
@@ -620,21 +611,12 @@
     <x:t xml:space="preserve">system_id</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">pms_archive.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联基础档案中的系统。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">问题类型ID</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">problem_type</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">关联基础档案中的问题类型。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">问题描述</x:t>
   </x:si>
   <x:si>
@@ -656,9 +638,6 @@
     <x:t xml:space="preserve">已处理完成</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">完成状态下填写的处置结果。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">跟进人ID</x:t>
   </x:si>
   <x:si>
@@ -677,9 +656,6 @@
     <x:t xml:space="preserve">0 低，1 中，2 高。</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">0 待处理，1 处理中，2 已完成，3 已关闭。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">逾期标记</x:t>
   </x:si>
   <x:si>
@@ -707,9 +683,6 @@
     <x:t xml:space="preserve">resolve_date</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">状态变为已完成时填写。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">关闭时间</x:t>
   </x:si>
   <x:si>
@@ -767,22 +740,10 @@
     <x:t xml:space="preserve">类型编码</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">档案类型编码。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">编码前缀</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">code_prefix</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SYS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">档案编码前缀。</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">类型名称</x:t>
@@ -1771,7 +1732,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -1814,6 +1775,27 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -2356,19 +2338,19 @@
       <x:c r="A9" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s">
-        <x:v>26</x:v>
+      <x:c r="B9" s="16" t="str">
+        <x:v>UNIQUE / 部分唯一索引</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>工号、手机号和关联关系保持全局唯一；角色编码、档案类型编码及前缀仅未删除数据唯一。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="16" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="16" t="str">
         <x:v>用户状态、角色删除标记、菜单路径、工单状态/跟进人、档案类型、操作日志模块与创建时间建索引。</x:v>
@@ -2376,32 +2358,32 @@
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A12" s="16" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B12" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A13" s="16" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="16" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="16" t="str">
         <x:v>初始化 SQL 包含管理员、业务菜单、组件工作台独立子菜单和基础档案。</x:v>
@@ -2441,7 +2423,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>257</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2455,328 +2437,328 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>258</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
-        <x:v>259</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>260</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>261</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>262</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>263</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>264</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>265</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7" t="s">
-        <x:v>266</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>267</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>268</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I12" s="9" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J12" s="9" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="I12" s="9" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J12" s="9" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2806,7 +2788,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>269</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2820,286 +2802,286 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7"/>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>270</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>271</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>272</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>273</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>274</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>275</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>276</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
-        <x:v>277</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>278</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>279</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>280</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H7" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>281</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>282</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>283</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>284</x:v>
+        <x:v>271</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>285</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>286</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
-        <x:v>287</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>288</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
-        <x:v>289</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>290</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
-        <x:v>291</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>292</x:v>
+        <x:v>279</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>293</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>294</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
-        <x:v>295</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>296</x:v>
+        <x:v>283</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
-        <x:v>297</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>298</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
-        <x:v>299</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>300</x:v>
+        <x:v>287</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
@@ -3130,28 +3112,28 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E14"/>
       <x:c r="F14"/>
       <x:c r="G14"/>
       <x:c r="H14" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I14" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J14" t="s">
-        <x:v>301</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3181,7 +3163,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>302</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3195,440 +3177,440 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7"/>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>303</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="7"/>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H5" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I5" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>304</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>305</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>306</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
-        <x:v>307</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>308</x:v>
+        <x:v>295</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D7" s="7"/>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>309</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>310</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>311</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>312</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
-        <x:v>313</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>314</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>315</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>316</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>312</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7"/>
       <x:c r="I9" s="8" t="s">
-        <x:v>317</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>318</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
-        <x:v>319</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>320</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I10" s="8" t="s">
-        <x:v>321</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>322</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>323</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>324</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I11" s="8" t="s">
-        <x:v>325</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>326</x:v>
+        <x:v>313</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1">
       <x:c r="A12" s="9" t="s">
-        <x:v>327</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>328</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I12" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>329</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
       <x:c r="A13" s="9" t="s">
-        <x:v>330</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>331</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I13" s="9" t="s">
-        <x:v>332</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>333</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="1" customFormat="1">
       <x:c r="A14" s="9" t="s">
-        <x:v>334</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B14" s="9" t="s">
-        <x:v>335</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D14" s="9"/>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I14" s="9" t="s">
-        <x:v>336</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="J14" s="9" t="s">
-        <x:v>337</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="1" customFormat="1">
       <x:c r="A15" s="9" t="s">
-        <x:v>338</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B15" s="9" t="s">
-        <x:v>339</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I15" s="10">
         <x:v>3600</x:v>
       </x:c>
       <x:c r="J15" s="9" t="s">
-        <x:v>340</x:v>
+        <x:v>327</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="1" customFormat="1">
       <x:c r="A16" s="9" t="s">
-        <x:v>341</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B16" s="9" t="s">
-        <x:v>298</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>239</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D16" s="9"/>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I16" s="9" t="s">
-        <x:v>342</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="J16" s="9" t="s">
-        <x:v>343</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="1" customFormat="1">
       <x:c r="A17" s="9" t="s">
-        <x:v>344</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B17" s="9" t="s">
-        <x:v>345</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C17" s="9" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D17" s="9"/>
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="9"/>
       <x:c r="G17" s="9"/>
       <x:c r="H17" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I17" s="9" t="s">
-        <x:v>346</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="J17" s="9" t="s">
-        <x:v>347</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="1" customFormat="1">
       <x:c r="A18" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B18" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C18" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D18" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9"/>
       <x:c r="G18" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H18" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I18" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J18" s="9" t="s">
-        <x:v>348</x:v>
+        <x:v>335</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3658,7 +3640,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>349</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -3672,134 +3654,134 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>350</x:v>
+        <x:v>337</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>351</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>352</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7" t="s">
-        <x:v>353</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="I5" s="8" t="s">
-        <x:v>353</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>354</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>355</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>356</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
@@ -3811,21 +3793,21 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>357</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>358</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>359</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
@@ -3834,7 +3816,7 @@
         <x:v>light</x:v>
       </x:c>
       <x:c r="I7" s="8" t="s">
-        <x:v>360</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
         <x:v>外观模式，当前仅支持浅色。</x:v>
@@ -3842,54 +3824,54 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I8" s="8" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="I8" s="8" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
@@ -3909,29 +3891,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>361</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F11" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H11" s="7"/>
       <x:c r="I11" s="8" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>362</x:v>
+        <x:v>349</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3961,193 +3943,193 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="G1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="J1" s="5" t="s">
-        <x:v>363</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>364</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>365</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>366</x:v>
+        <x:v>353</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>367</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>312</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>368</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>369</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>370</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>371</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>372</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
-        <x:v>373</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>374</x:v>
+        <x:v>361</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>375</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>206</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="8" t="s">
-        <x:v>376</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="J7" s="7" t="str">
         <x:v>消息正文，最长 1000 个字符。</x:v>
@@ -4155,160 +4137,160 @@
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>377</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>378</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
       <x:c r="H8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I8" s="8" t="s">
-        <x:v>353</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>379</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>380</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>381</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
-        <x:v>382</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>383</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>384</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H11" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A12" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B12" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E12" s="7"/>
       <x:c r="F12" s="7"/>
       <x:c r="G12" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H12" s="7" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I12" s="8" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="I12" s="8" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A13" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B13" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C13" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E13" s="7"/>
       <x:c r="F13" s="7"/>
       <x:c r="G13" s="7"/>
       <x:c r="H13" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I13" s="8" t="s">
-        <x:v>382</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="J13" s="7" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4332,13 +4314,13 @@
   <x:sheetData>
     <x:row r="1" s="12" customFormat="1">
       <x:c r="A1" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="B1" s="13" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C1" s="13" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
         <x:v>2</x:v>
@@ -4349,13 +4331,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="9" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="C2" s="9" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D2" s="9" t="s">
-        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4363,13 +4345,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D3" s="9" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4377,13 +4359,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4391,13 +4373,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4405,13 +4387,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="9" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4419,13 +4401,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="C7" s="9" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D7" s="9" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4433,13 +4415,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="9" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4447,13 +4429,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="9" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D9" s="9" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4461,13 +4443,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D10" s="9" t="s">
-        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4475,13 +4457,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="9" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D11" s="9" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4489,13 +4471,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4503,19 +4485,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D13" s="9" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="s">
-        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a184306063848ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd236f44135a48fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4539,7 +4521,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -4553,354 +4535,354 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A7" s="7" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A8" s="7" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H8" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I8" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I9" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A10" s="7" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I10" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="7" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B12" s="9" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C12" s="9" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D12" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9"/>
       <x:c r="G12" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H12" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I12" s="10">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J13" s="9" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B14" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D14" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9"/>
       <x:c r="H14" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I14" s="10" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J14" s="9" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4943,298 +4925,310 @@
     <x:col min="2" max="2" width="9.411765098571777" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="12.647058486938477" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="4.117647171020508" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="7.352941036224365" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="16" style="2" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.852941513061523" style="2" customWidth="1"/>
     <x:col min="7" max="7" width="7.352941036224365" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="5.735294342041016" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="20.58823585510254" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="15.588234901428223" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="48" style="2" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="9" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="3" t="s">
+    <x:row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A1" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B1" s="18"/>
+      <x:c r="C1" s="18"/>
+      <x:c r="D1" s="18"/>
+      <x:c r="E1" s="18"/>
+      <x:c r="F1" s="18"/>
+      <x:c r="G1" s="18"/>
+      <x:c r="H1" s="18"/>
+      <x:c r="I1" s="18"/>
+      <x:c r="J1" s="19"/>
+    </x:row>
+    <x:row r="2" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="20" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G2" s="20" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H2" s="20" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I2" s="20" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="J2" s="20" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A3" s="21" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="21" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="21" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F3" s="21"/>
+      <x:c r="G3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H3" s="21" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="I3" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="21" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A4" s="21" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="5"/>
-    </x:row>
-    <x:row r="2" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A2" s="6" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A3" s="7" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I3" s="8">
+      <x:c r="C4" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="str">
+        <x:v>有效数据唯一</x:v>
+      </x:c>
+      <x:c r="F4" s="21"/>
+      <x:c r="G4" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="21"/>
+      <x:c r="I4" s="22" t="str">
+        <x:v>admin</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="str">
+        <x:v>角色业务编码；未删除数据唯一，软删除后可复用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A5" s="21" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B5" s="21" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E5" s="21"/>
+      <x:c r="F5" s="21"/>
+      <x:c r="G5" s="21"/>
+      <x:c r="H5" s="21"/>
+      <x:c r="I5" s="22" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="J5" s="21" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A6" s="21" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C6" s="21" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D6" s="21"/>
+      <x:c r="E6" s="21"/>
+      <x:c r="F6" s="21"/>
+      <x:c r="G6" s="21"/>
+      <x:c r="H6" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I6" s="22" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A7" s="21" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="21"/>
+      <x:c r="F7" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I7" s="22">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A4" s="7" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F4" s="7"/>
-      <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H4" s="7"/>
-      <x:c r="I4" s="8" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A5" s="7" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E5" s="7"/>
-      <x:c r="F5" s="7"/>
-      <x:c r="G5" s="7"/>
-      <x:c r="H5" s="7"/>
-      <x:c r="I5" s="8" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>146</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A6" s="7" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D6" s="7"/>
-      <x:c r="E6" s="7"/>
-      <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7"/>
-      <x:c r="H6" s="7" t="s">
+      <x:c r="J7" s="21" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A8" s="21" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>151</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A7" s="7" t="s">
+      <x:c r="B8" s="21" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
+      <x:c r="D8" s="21"/>
+      <x:c r="E8" s="21"/>
+      <x:c r="F8" s="21" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C7" s="7" t="s">
+      <x:c r="G8" s="21"/>
+      <x:c r="H8" s="21" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D7" s="7"/>
-      <x:c r="E7" s="7"/>
-      <x:c r="F7" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I7" s="8">
+      <x:c r="I8" s="22">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>124</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A8" s="7" t="s">
+      <x:c r="J8" s="21" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="s">
+    </x:row>
+    <x:row r="9" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A9" s="21" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I8" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
+      <x:c r="B9" s="21" t="s">
         <x:v>127</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A9" s="7" t="s">
+      <x:c r="C9" s="21" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E9" s="21"/>
+      <x:c r="F9" s="21"/>
+      <x:c r="G9" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H9" s="21" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="s">
+      <x:c r="I9" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H9" s="7" t="s">
+    </x:row>
+    <x:row r="10" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A10" s="21" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="I9" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
+      <x:c r="B10" s="21" t="s">
         <x:v>131</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A10" s="7" t="s">
+      <x:c r="C10" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E10" s="21"/>
+      <x:c r="F10" s="21"/>
+      <x:c r="G10" s="21"/>
+      <x:c r="H10" s="21" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="I10" s="22" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
-      <x:c r="H10" s="7" t="s">
+      <x:c r="J10" s="21" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="s">
+    </x:row>
+    <x:row r="11" s="11" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A11" s="21" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="J10" s="7" t="s">
+      <x:c r="B11" s="21" t="s">
         <x:v>136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" s="11" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A11" s="7" t="s">
+      <x:c r="C11" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E11" s="21"/>
+      <x:c r="F11" s="21"/>
+      <x:c r="G11" s="21"/>
+      <x:c r="H11" s="21" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I11" s="22" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J11" s="21" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="I11" s="8" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>139</x:v>
-      </x:c>
+    </x:row>
+    <x:row r="12" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A12" s="23"/>
+      <x:c r="B12" s="23"/>
+      <x:c r="C12" s="23"/>
+      <x:c r="D12" s="23"/>
+      <x:c r="E12" s="23"/>
+      <x:c r="F12" s="23"/>
+      <x:c r="G12" s="23"/>
+      <x:c r="H12" s="23"/>
+      <x:c r="I12" s="23"/>
+      <x:c r="J12" s="23"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5263,7 +5257,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5277,150 +5271,150 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="7" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
@@ -5440,29 +5434,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5492,7 +5486,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5506,137 +5500,137 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7"/>
       <x:c r="F4" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G4" s="7"/>
       <x:c r="H4" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I4" s="8">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7"/>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="7"/>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="8" t="str">
@@ -5648,48 +5642,48 @@
     </x:row>
     <x:row r="7" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A7" s="7" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E7" s="7"/>
       <x:c r="F7" s="7"/>
       <x:c r="G7" s="7"/>
       <x:c r="H7" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I7" s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c r="J7" s="7" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="8" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A8" s="7" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D8" s="7"/>
       <x:c r="E8" s="7"/>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H8" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
         <x:v>/system/design-system?category=base</x:v>
@@ -5700,46 +5694,46 @@
     </x:row>
     <x:row r="9" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A9" s="7" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" s="7"/>
       <x:c r="E9" s="7"/>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
       <x:c r="H9" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I9" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J9" s="7" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="30" customHeight="1">
       <x:c r="A10" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E10" s="7"/>
       <x:c r="F10" s="7"/>
       <x:c r="G10" s="7"/>
       <x:c r="H10" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I10" s="8" t="n">
         <x:v>45</x:v>
@@ -5750,160 +5744,160 @@
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A11" s="7" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
       <x:c r="G11" s="7"/>
       <x:c r="H11" s="7" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I11" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="9" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="D12" s="9"/>
       <x:c r="E12" s="9"/>
       <x:c r="F12" s="9" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G12" s="9"/>
       <x:c r="H12" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I12" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="9" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B13" s="9" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C13" s="9" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G13" s="9"/>
       <x:c r="H13" s="9" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I13" s="9">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="9" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B14" s="9" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C14" s="9" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D14" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9"/>
       <x:c r="G14" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H14" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I14" s="9">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="9" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="9" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B15" s="9" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C15" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D15" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9"/>
       <x:c r="G15" s="9"/>
       <x:c r="H15" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I15" s="9" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J15" s="9" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="I15" s="9" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B16" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C16" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D16" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9"/>
       <x:c r="G16" s="9"/>
       <x:c r="H16" s="9" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I16" s="9" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J16" s="9" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5933,7 +5927,7 @@
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -5947,150 +5941,150 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A2" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="6" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="6" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="6" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="6" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="6" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F3" s="7"/>
       <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I3" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="7" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="8">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="7" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A5" s="7" t="s">
-        <x:v>188</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>189</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="8">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J5" s="7" t="s">
-        <x:v>190</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E6" s="7"/>
       <x:c r="F6" s="7"/>
       <x:c r="G6" s="7"/>
       <x:c r="H6" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I6" s="8" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J6" s="7" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="7" s="1" customFormat="1">
@@ -6110,29 +6104,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G8" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="8" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J8" s="7" t="s">
-        <x:v>195</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6152,580 +6146,580 @@
     <x:col min="3" max="3" width="13.29411792755127" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="4.117647171020508" style="2" customWidth="1"/>
     <x:col min="5" max="5" width="7.352941036224365" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="10.529411315917969" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="18" style="2" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="7.352941036224365" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="6.411764621734619" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="19.117647171020508" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="46.02941131591797" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="58" style="2" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="55.764705657958984" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" s="1" customFormat="1">
-      <x:c r="A1" s="3" t="s">
+    <x:row r="1" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A1" s="17" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B1" s="18"/>
+      <x:c r="C1" s="18"/>
+      <x:c r="D1" s="18"/>
+      <x:c r="E1" s="18"/>
+      <x:c r="F1" s="18"/>
+      <x:c r="G1" s="18"/>
+      <x:c r="H1" s="18"/>
+      <x:c r="I1" s="18"/>
+      <x:c r="J1" s="19"/>
+    </x:row>
+    <x:row r="2" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="20" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G2" s="20" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H2" s="20" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I2" s="20" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="J2" s="20" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A3" s="21" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B3" s="21" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C3" s="21" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F3" s="21"/>
+      <x:c r="G3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H3" s="21" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="I3" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="21" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A4" s="21" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="21"/>
+      <x:c r="F4" s="21" t="str">
+        <x:v>pms_archive.id</x:v>
+      </x:c>
+      <x:c r="G4" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="21"/>
+      <x:c r="I4" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="str">
+        <x:v>外键关联启用的系统档案；历史停用档案仍保留展示。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A5" s="21" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="5"/>
-    </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A2" s="6" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A3" s="7" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I3" s="8">
+      <x:c r="B5" s="21" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E5" s="21"/>
+      <x:c r="F5" s="21" t="str">
+        <x:v>pms_archive.id</x:v>
+      </x:c>
+      <x:c r="G5" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H5" s="21"/>
+      <x:c r="I5" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J5" s="21" t="str">
+        <x:v>外键关联启用的问题类型档案；历史停用档案仍保留展示。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A6" s="21" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C6" s="21" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E6" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F6" s="21"/>
+      <x:c r="G6" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H6" s="21"/>
+      <x:c r="I6" s="22" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="str">
+        <x:v>工单问题描述；有效数据（is_deleted = 0）按 md5(problem_desc) 唯一。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A7" s="21" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="21"/>
+      <x:c r="F7" s="21"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I7" s="22" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="str">
+        <x:v>状态变为已解决时填写的处置结果。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A8" s="21" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E8" s="21"/>
+      <x:c r="F8" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H8" s="21"/>
+      <x:c r="I8" s="22">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A4" s="7" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
+      <x:c r="J8" s="21" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A9" s="21" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E9" s="21"/>
+      <x:c r="F9" s="21"/>
+      <x:c r="G9" s="21"/>
+      <x:c r="H9" s="21" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I9" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A10" s="21" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B10" s="21" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E10" s="21"/>
+      <x:c r="F10" s="21"/>
+      <x:c r="G10" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="I10" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="21" t="str">
+        <x:v>工单状态：0 待处理、1 处理中、2 已解决、3 已关闭，只允许按顺序流转。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A11" s="21" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B11" s="21" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E11" s="21"/>
+      <x:c r="F11" s="21"/>
+      <x:c r="G11" s="21"/>
+      <x:c r="H11" s="21" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="21" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A12" s="21" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D12" s="21"/>
+      <x:c r="E12" s="21"/>
+      <x:c r="F12" s="21"/>
+      <x:c r="G12" s="21"/>
+      <x:c r="H12" s="21" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="E4" s="7"/>
-      <x:c r="F4" s="7" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H4" s="7"/>
-      <x:c r="I4" s="8">
+      <x:c r="I12" s="22" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="J12" s="21" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A13" s="21" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B13" s="21" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D13" s="21"/>
+      <x:c r="E13" s="21"/>
+      <x:c r="F13" s="21"/>
+      <x:c r="G13" s="21"/>
+      <x:c r="H13" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I13" s="21" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="J13" s="21" t="str">
+        <x:v>状态变为已解决时填写。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A14" s="21" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D14" s="21"/>
+      <x:c r="E14" s="21"/>
+      <x:c r="F14" s="21"/>
+      <x:c r="G14" s="21"/>
+      <x:c r="H14" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I14" s="21" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="J14" s="21" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A15" s="21" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E15" s="21"/>
+      <x:c r="F15" s="21"/>
+      <x:c r="G15" s="21"/>
+      <x:c r="H15" s="21"/>
+      <x:c r="I15" s="21" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="J15" s="21" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A16" s="21" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B16" s="21" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D16" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E16" s="21"/>
+      <x:c r="F16" s="21"/>
+      <x:c r="G16" s="21"/>
+      <x:c r="H16" s="21"/>
+      <x:c r="I16" s="21" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="J16" s="21" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A17" s="21" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B17" s="21" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D17" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E17" s="21"/>
+      <x:c r="F17" s="21"/>
+      <x:c r="G17" s="21"/>
+      <x:c r="H17" s="21"/>
+      <x:c r="I17" s="21" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="J17" s="21" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A18" s="21" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B18" s="21" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D18" s="21"/>
+      <x:c r="E18" s="21"/>
+      <x:c r="F18" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G18" s="21"/>
+      <x:c r="H18" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I18" s="21">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>200</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A5" s="7" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
+      <x:c r="J18" s="21" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A19" s="21" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B19" s="21" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C19" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D19" s="21"/>
+      <x:c r="E19" s="21"/>
+      <x:c r="F19" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G19" s="21"/>
+      <x:c r="H19" s="21" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E5" s="7"/>
-      <x:c r="F5" s="7" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H5" s="7"/>
-      <x:c r="I5" s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>203</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A6" s="7" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E6" s="7" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="H6" s="7"/>
-      <x:c r="I6" s="8" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="str">
-        <x:v>工单问题描述；有效数据（is_deleted = 0）按 md5(problem_desc) 唯一。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A7" s="7" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D7" s="7"/>
-      <x:c r="E7" s="7"/>
-      <x:c r="F7" s="7"/>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I7" s="8" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>211</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A8" s="7" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G8" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H8" s="7"/>
-      <x:c r="I8" s="8">
+      <x:c r="I19" s="21">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>214</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A9" s="7" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I9" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>217</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A10" s="7" t="s">
+      <x:c r="J19" s="21" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A20" s="21" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B20" s="21" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C20" s="21" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H10" s="7" t="s">
+      <x:c r="D20" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E20" s="21"/>
+      <x:c r="F20" s="21"/>
+      <x:c r="G20" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H20" s="21" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="21" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A21" s="21" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="I10" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>218</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A11" s="7" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="I11" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>221</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="17">
-      <x:c r="A12" s="7" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D12" s="7"/>
-      <x:c r="E12" s="7"/>
-      <x:c r="F12" s="7"/>
-      <x:c r="G12" s="7"/>
-      <x:c r="H12" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I12" s="8" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="s">
-        <x:v>225</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="9" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D13" s="9"/>
-      <x:c r="E13" s="9"/>
-      <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I13" s="9" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>228</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="9" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="B14" s="9" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="C14" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D14" s="9"/>
-      <x:c r="E14" s="9"/>
-      <x:c r="F14" s="9"/>
-      <x:c r="G14" s="9"/>
-      <x:c r="H14" s="9" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I14" s="9" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="J14" s="9" t="s">
-        <x:v>232</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="9" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="B15" s="9" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C15" s="9" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D15" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E15" s="9"/>
-      <x:c r="F15" s="9"/>
-      <x:c r="G15" s="9"/>
-      <x:c r="H15" s="9"/>
-      <x:c r="I15" s="9" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="J15" s="9" t="s">
-        <x:v>236</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="9" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="B16" s="9" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="C16" s="9" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D16" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E16" s="9"/>
-      <x:c r="F16" s="9"/>
-      <x:c r="G16" s="9"/>
-      <x:c r="H16" s="9"/>
-      <x:c r="I16" s="9" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="J16" s="9" t="s">
-        <x:v>241</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="9" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="B17" s="9" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="C17" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D17" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E17" s="9"/>
-      <x:c r="F17" s="9"/>
-      <x:c r="G17" s="9"/>
-      <x:c r="H17" s="9"/>
-      <x:c r="I17" s="9" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="J17" s="9" t="s">
-        <x:v>245</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="9" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B18" s="9" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C18" s="9" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D18" s="9"/>
-      <x:c r="E18" s="9"/>
-      <x:c r="F18" s="9" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G18" s="9"/>
-      <x:c r="H18" s="9" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I18" s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J18" s="9" t="s">
-        <x:v>124</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="9" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B19" s="9" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C19" s="9" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D19" s="9"/>
-      <x:c r="E19" s="9"/>
-      <x:c r="F19" s="9" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G19" s="9"/>
-      <x:c r="H19" s="9" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I19" s="9">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J19" s="9" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="9" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="B20" s="9" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C20" s="9" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D20" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E20" s="9"/>
-      <x:c r="F20" s="9"/>
-      <x:c r="G20" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H20" s="9" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="I20" s="9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="9" t="s">
+      <x:c r="B21" s="21" t="s">
         <x:v>131</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="9" t="s">
+      <x:c r="C21" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D21" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E21" s="21"/>
+      <x:c r="F21" s="21"/>
+      <x:c r="G21" s="21"/>
+      <x:c r="H21" s="21" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B21" s="9" t="s">
+      <x:c r="I21" s="21" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C21" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D21" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E21" s="9"/>
-      <x:c r="F21" s="9"/>
-      <x:c r="G21" s="9"/>
-      <x:c r="H21" s="9" t="s">
+      <x:c r="J21" s="21" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="I21" s="9" t="s">
+    </x:row>
+    <x:row r="22" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A22" s="21" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="J21" s="9" t="s">
+      <x:c r="B22" s="21" t="s">
         <x:v>136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="9" t="s">
+      <x:c r="C22" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D22" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E22" s="21"/>
+      <x:c r="F22" s="21"/>
+      <x:c r="G22" s="21"/>
+      <x:c r="H22" s="21" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I22" s="21" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J22" s="21" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="B22" s="9" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C22" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D22" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E22" s="9"/>
-      <x:c r="F22" s="9"/>
-      <x:c r="G22" s="9"/>
-      <x:c r="H22" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="I22" s="9" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J22" s="9" t="s">
-        <x:v>139</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6744,328 +6738,340 @@
     <x:col min="2" max="2" width="10" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="13.29411792755127" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="4.117647171020508" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="7.352941036224365" style="2" customWidth="1"/>
+    <x:col min="5" max="5" width="16" style="2" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.852941513061523" style="2" customWidth="1"/>
     <x:col min="7" max="7" width="7.352941036224365" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="6.411764621734619" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="19.117647171020508" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="16.882352828979492" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="48" style="2" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="55.764705657958984" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" s="1" customFormat="1">
-      <x:c r="A1" s="3" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="5"/>
-    </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A2" s="6" t="s">
+    <x:row r="1" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A1" s="17" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B1" s="18"/>
+      <x:c r="C1" s="18"/>
+      <x:c r="D1" s="18"/>
+      <x:c r="E1" s="18"/>
+      <x:c r="F1" s="18"/>
+      <x:c r="G1" s="18"/>
+      <x:c r="H1" s="18"/>
+      <x:c r="I1" s="18"/>
+      <x:c r="J1" s="19"/>
+    </x:row>
+    <x:row r="2" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A2" s="20" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="s">
+      <x:c r="D2" s="20" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="s">
+      <x:c r="E2" s="20" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="s">
+      <x:c r="F2" s="20" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="s">
+      <x:c r="G2" s="20" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="s">
+      <x:c r="H2" s="20" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="s">
+      <x:c r="I2" s="20" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="s">
+      <x:c r="J2" s="20" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="s">
+    </x:row>
+    <x:row r="3" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A3" s="21" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="J2" s="6" t="s">
+      <x:c r="B3" s="21" t="s">
         <x:v>86</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A3" s="7" t="s">
+      <x:c r="C3" s="21" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B3" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C3" s="7" t="s">
+      <x:c r="D3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F3" s="21"/>
+      <x:c r="G3" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H3" s="21" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D3" s="7" t="s">
+      <x:c r="I3" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="21" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="I3" s="8">
+    </x:row>
+    <x:row r="4" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A4" s="21" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="str">
+        <x:v>有效数据唯一</x:v>
+      </x:c>
+      <x:c r="F4" s="21"/>
+      <x:c r="G4" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="21"/>
+      <x:c r="I4" s="22" t="str">
+        <x:v>001</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="str">
+        <x:v>档案类型编码；未删除数据唯一，软删除后可复用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A5" s="21" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B5" s="21" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="str">
+        <x:v>有效数据唯一</x:v>
+      </x:c>
+      <x:c r="F5" s="21"/>
+      <x:c r="G5" s="21" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H5" s="21"/>
+      <x:c r="I5" s="22" t="str">
+        <x:v>SYS</x:v>
+      </x:c>
+      <x:c r="J5" s="21" t="str">
+        <x:v>档案编码前缀；未删除数据唯一，软删除后可复用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A6" s="21" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C6" s="21" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E6" s="21"/>
+      <x:c r="F6" s="21"/>
+      <x:c r="G6" s="21"/>
+      <x:c r="H6" s="21"/>
+      <x:c r="I6" s="22" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A7" s="21" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C7" s="21" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E7" s="21"/>
+      <x:c r="F7" s="21"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="21" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I7" s="22">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A4" s="7" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F4" s="7"/>
-      <x:c r="G4" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H4" s="7"/>
-      <x:c r="I4" s="8" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>249</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A5" s="7" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F5" s="7"/>
-      <x:c r="G5" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H5" s="7"/>
-      <x:c r="I5" s="8" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>253</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A6" s="7" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D6" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E6" s="7"/>
-      <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7"/>
-      <x:c r="H6" s="7"/>
-      <x:c r="I6" s="8" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>256</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A7" s="7" t="s">
+      <x:c r="J7" s="21" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A8" s="21" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D8" s="21"/>
+      <x:c r="E8" s="21"/>
+      <x:c r="F8" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G8" s="21"/>
+      <x:c r="H8" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I8" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A9" s="21" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D9" s="21"/>
+      <x:c r="E9" s="21"/>
+      <x:c r="F9" s="21" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G9" s="21"/>
+      <x:c r="H9" s="21" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="I9" s="22">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A10" s="21" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B10" s="21" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E7" s="7"/>
-      <x:c r="F7" s="7"/>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I7" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>115</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A8" s="7" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I8" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>124</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A9" s="7" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D9" s="7"/>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="7" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I9" s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A10" s="7" t="s">
+      <x:c r="D10" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E10" s="21"/>
+      <x:c r="F10" s="21"/>
+      <x:c r="G10" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="s">
+      <x:c r="I10" s="22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="21" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H10" s="7" t="s">
+    </x:row>
+    <x:row r="11" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A11" s="21" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="I10" s="8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
+      <x:c r="B11" s="21" t="s">
         <x:v>131</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" s="1" customFormat="1" ht="17" customHeight="1">
-      <x:c r="A11" s="7" t="s">
+      <x:c r="C11" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E11" s="21"/>
+      <x:c r="F11" s="21"/>
+      <x:c r="G11" s="21"/>
+      <x:c r="H11" s="21" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="s">
+      <x:c r="I11" s="22" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7" t="s">
+      <x:c r="J11" s="21" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="s">
+    </x:row>
+    <x:row r="12" s="1" customFormat="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A12" s="21" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="J11" s="7" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>136</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" s="1" customFormat="1">
-      <x:c r="A12" s="9" t="s">
+      <x:c r="C12" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E12" s="21"/>
+      <x:c r="F12" s="21"/>
+      <x:c r="G12" s="21"/>
+      <x:c r="H12" s="21" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="I12" s="21" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J12" s="21" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C12" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E12" s="9"/>
-      <x:c r="F12" s="9"/>
-      <x:c r="G12" s="9"/>
-      <x:c r="H12" s="9" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="I12" s="9" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="J12" s="9" t="s">
-        <x:v>139</x:v>
-      </x:c>
+    </x:row>
+    <x:row r="13" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A13" s="23"/>
+      <x:c r="B13" s="23"/>
+      <x:c r="C13" s="23"/>
+      <x:c r="D13" s="23"/>
+      <x:c r="E13" s="23"/>
+      <x:c r="F13" s="23"/>
+      <x:c r="G13" s="23"/>
+      <x:c r="H13" s="23"/>
+      <x:c r="I13" s="23"/>
+      <x:c r="J13" s="23"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
